--- a/config/templates/material-info/accessory_split_2.xlsx
+++ b/config/templates/material-info/accessory_split_2.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="114">
   <si>
     <t>物料标签打印配置 — 修改「当前值」列后保存，刷新打印页即自动生效</t>
   </si>
@@ -162,10 +162,22 @@
     <t>各信息字段（编号/布卡号等）的字体大小</t>
   </si>
   <si>
+    <t>字段标签字号</t>
+  </si>
+  <si>
+    <t>字段标签文字（如物料编码、颜色）的字体大小</t>
+  </si>
+  <si>
     <t>字段内容最多行数</t>
   </si>
   <si>
     <t>普通字段内容超出行数时自动截断，0 = 不限制</t>
+  </si>
+  <si>
+    <t>颜色最多行数</t>
+  </si>
+  <si>
+    <t>颜色字段内容超出行数时自动截断，0 = 不限制</t>
   </si>
   <si>
     <t>备注最多行数</t>
@@ -370,7 +382,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -417,13 +429,6 @@
       <color rgb="FF333333"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -912,148 +917,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1442,7 +1447,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1706,7 +1711,7 @@
         <v>42</v>
       </c>
       <c r="C16" s="12">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="D16" s="13">
         <v>8.5</v>
@@ -1726,16 +1731,16 @@
         <v>44</v>
       </c>
       <c r="C17" s="10">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D17" s="11">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>45</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:6">
@@ -1746,10 +1751,10 @@
         <v>46</v>
       </c>
       <c r="C18" s="12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="13" t="s">
         <v>47</v>
@@ -1766,121 +1771,121 @@
         <v>48</v>
       </c>
       <c r="C19" s="10">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="D19" s="11">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>49</v>
       </c>
       <c r="F19" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="1:6">
+      <c r="A20" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="20" ht="20" customHeight="1" spans="1:6">
-      <c r="A20" s="8" t="s">
+      <c r="C20" s="12">
+        <v>4</v>
+      </c>
+      <c r="D20" s="13">
+        <v>4</v>
+      </c>
+      <c r="E20" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
+      <c r="F20" s="13" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:6">
       <c r="A21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="10">
+        <v>52</v>
+      </c>
+      <c r="D21" s="11">
+        <v>52</v>
+      </c>
+      <c r="E21" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="F21" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D21" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E21" s="11" t="s">
+    </row>
+    <row r="22" ht="20" customHeight="1" spans="1:6">
+      <c r="A22" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:6">
+      <c r="A23" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F23" s="11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1" spans="1:6">
-      <c r="A22" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="3" t="s">
+    <row r="24" ht="18" customHeight="1" spans="1:6">
+      <c r="A24" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="12">
+      <c r="B24" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="12">
         <v>20</v>
       </c>
-      <c r="D22" s="13">
+      <c r="D24" s="13">
         <v>22</v>
       </c>
-      <c r="E22" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F22" s="13" t="s">
+      <c r="E24" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="13" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="23" ht="20" customHeight="1" spans="1:6">
-      <c r="A23" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-    </row>
-    <row r="24" ht="18" customHeight="1" spans="1:6">
-      <c r="A24" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" s="10">
-        <v>1</v>
-      </c>
-      <c r="D24" s="11">
-        <v>2</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1" spans="1:6">
-      <c r="A25" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B25" s="3" t="s">
+    <row r="25" ht="20" customHeight="1" spans="1:6">
+      <c r="A25" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="12">
-        <v>0</v>
-      </c>
-      <c r="D25" s="13">
-        <v>6</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>22</v>
-      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:6">
       <c r="A26" s="5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>64</v>
@@ -1889,7 +1894,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>65</v>
@@ -1898,91 +1903,91 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1" spans="1:6">
-      <c r="A27" s="8" t="s">
+    <row r="27" ht="18" customHeight="1" spans="1:6">
+      <c r="A27" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
+      <c r="C27" s="12">
+        <v>0</v>
+      </c>
+      <c r="D27" s="13">
+        <v>6</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="28" ht="18" customHeight="1" spans="1:6">
       <c r="A28" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="10">
+        <v>1</v>
+      </c>
+      <c r="D28" s="11">
+        <v>4</v>
+      </c>
+      <c r="E28" s="11" t="s">
         <v>69</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>70</v>
       </c>
       <c r="F28" s="11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1" spans="1:6">
-      <c r="A29" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>13</v>
-      </c>
+    <row r="29" ht="20" customHeight="1" spans="1:6">
+      <c r="A29" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:6">
       <c r="A30" s="5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B30" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C30" s="10">
-        <v>6</v>
-      </c>
-      <c r="D30" s="11">
-        <v>6</v>
+      <c r="D30" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>74</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:6">
       <c r="A31" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>75</v>
       </c>
       <c r="C31" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" s="13" t="s">
         <v>76</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>77</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>13</v>
@@ -1990,21 +1995,61 @@
     </row>
     <row r="32" ht="18" customHeight="1" spans="1:6">
       <c r="A32" s="5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B32" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="10">
+        <v>6</v>
+      </c>
+      <c r="D32" s="11">
+        <v>6</v>
+      </c>
+      <c r="E32" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="F32" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1" spans="1:6">
+      <c r="A33" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D32" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F32" s="11" t="s">
+      <c r="C33" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1" spans="1:6">
+      <c r="A34" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="F34" s="11" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2015,9 +2060,9 @@
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A29:F29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2037,32 +2082,32 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
@@ -2070,13 +2115,13 @@
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:4">
       <c r="A4" s="5" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D4" s="5">
         <v>2</v>
@@ -2084,13 +2129,13 @@
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D5" s="3">
         <v>3</v>
@@ -2098,13 +2143,13 @@
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D6" s="5">
         <v>4</v>
@@ -2112,13 +2157,13 @@
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:4">
       <c r="A7" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D7" s="3">
         <v>5</v>
@@ -2126,13 +2171,13 @@
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:4">
       <c r="A8" s="5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D8" s="5">
         <v>6</v>
@@ -2140,13 +2185,13 @@
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:4">
       <c r="A9" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D9" s="3">
         <v>7</v>
@@ -2154,13 +2199,13 @@
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:4">
       <c r="A10" s="5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D10" s="5">
         <v>8</v>
@@ -2168,13 +2213,13 @@
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:4">
       <c r="A11" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D11" s="3">
         <v>9</v>
@@ -2182,13 +2227,13 @@
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D12" s="5">
         <v>10</v>
@@ -2196,13 +2241,13 @@
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:4">
       <c r="A13" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D13" s="3">
         <v>11</v>
@@ -2210,13 +2255,13 @@
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:4">
       <c r="A14" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D14" s="5">
         <v>12</v>
@@ -2224,13 +2269,13 @@
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D15" s="3">
         <v>13</v>
